--- a/Eugen-tasks.xlsx
+++ b/Eugen-tasks.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eugra\Desktop\c#\HelloWorld\pyt\python_scripting\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2482A165-0F68-4DD3-811F-306985338B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>#</t>
   </si>
@@ -36,8 +45,9 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>- zip file with DataSetA, B, C, D
 A script that does the following:
@@ -47,16 +57,18 @@
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
         <i/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>you not the script, eg in the .json file we wanna change unit for VehicleSpeed to mph</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">) from each file (txt, json, dbc, xml) and modifies a value or field
    Bonus: allow the user to search and choose a data type instead of random
@@ -68,24 +80,27 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">The script should have arguments but also work without
 The script should handle txt, json, dbc, xml file </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
         <b/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>ONLY</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
 Good error handling. (Try blocks)</t>
@@ -100,35 +115,29 @@
 requirements.txt</t>
   </si>
   <si>
-    <t>- jsonA + jsonB are datafiles for ECUs and signals
-- jsonA holds all signal data and their current status
-- jsonB holds ECU configuration and running tasks
-A script that does the following:
-1. Verifies that the ECU states in B match the signal statuses in A, if not flag this
-2. Allows adding new ECUs or signals, and should populate both A and B with correct info
-3. Add all info into a simple database (updates both A &amp; B, then commits to DB)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">The script should have arguments but also work without
 The script should handle json files </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
         <b/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t>ONLY</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Arial"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
 Good error handling. (Try blocks)</t>
@@ -138,37 +147,74 @@
     <t>jsonA.json
 jsonB.json
 requirements.txt</t>
+  </si>
+  <si>
+    <t>A script that does the following:</t>
+  </si>
+  <si>
+    <t>1. Verifies that the ECU states in B match the signal statuses in A, if not flag this</t>
+  </si>
+  <si>
+    <t>2. Allows adding new ECUs or signals, and should populate both A and B with correct info</t>
+  </si>
+  <si>
+    <t>3. Add all info into a simple database (updates both A &amp; B, then commits to DB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jsonA holds all signal data and their current status</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jsonB holds ECU configuration and running tasks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -176,9 +222,21 @@
         <bgColor rgb="FFF3F3F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -192,48 +250,53 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -423,26 +486,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.13"/>
-    <col customWidth="1" min="2" max="2" width="71.0"/>
-    <col customWidth="1" min="3" max="3" width="21.0"/>
-    <col customWidth="1" min="4" max="4" width="16.25"/>
-    <col customWidth="1" min="5" max="5" width="23.13"/>
-    <col customWidth="1" min="6" max="6" width="48.0"/>
-    <col customWidth="1" min="7" max="7" width="17.75"/>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="77.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="54.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,9 +531,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" ht="148.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
@@ -475,31 +541,58 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" ht="184.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>